--- a/Project Group Formation (1)(1-16).xlsx
+++ b/Project Group Formation (1)(1-16).xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Git Backup\2GITHUB\AEC_ML_Batch_2_August_2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB8D90F-77BA-4E29-BEED-70D8670F0940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7AE15FA-7792-4F5B-B2E2-CF180C209390}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="302" uniqueCount="251">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="258">
   <si>
     <t>Start time</t>
   </si>
@@ -140,9 +140,6 @@
     <t>BSDS</t>
   </si>
   <si>
-    <t>Academic Risk &amp; Engagement Prediction</t>
-  </si>
-  <si>
     <t>32240524009</t>
   </si>
   <si>
@@ -227,9 +224,6 @@
     <t>8116777544</t>
   </si>
   <si>
-    <t>ForestWatch: An AI powered System for Early Detection of Illegal Tree Felling</t>
-  </si>
-  <si>
     <t>108003240046</t>
   </si>
   <si>
@@ -320,9 +314,6 @@
     <t>6207929936</t>
   </si>
   <si>
-    <t>Student Marks Prediction</t>
-  </si>
-  <si>
     <t>108427240077</t>
   </si>
   <si>
@@ -386,9 +377,6 @@
     <t>9093091618</t>
   </si>
   <si>
-    <t>Whatsapp chat analyzer</t>
-  </si>
-  <si>
     <t>108321240013</t>
   </si>
   <si>
@@ -467,9 +455,6 @@
     <t>6296916217</t>
   </si>
   <si>
-    <t>Customer Purchase Prediction</t>
-  </si>
-  <si>
     <t>108311240001</t>
   </si>
   <si>
@@ -539,9 +524,6 @@
     <t>9641047967</t>
   </si>
   <si>
-    <t>House Price Prediction</t>
-  </si>
-  <si>
     <t>108321240004</t>
   </si>
   <si>
@@ -686,9 +668,6 @@
     <t>9002757086</t>
   </si>
   <si>
-    <t>108247240057</t>
-  </si>
-  <si>
     <t>Ritika Mandal</t>
   </si>
   <si>
@@ -776,9 +755,6 @@
     <t>BSC (DS)</t>
   </si>
   <si>
-    <t>TBD</t>
-  </si>
-  <si>
     <t>Community Signal AI</t>
   </si>
   <si>
@@ -789,6 +765,51 @@
   </si>
   <si>
     <t>Group Number</t>
+  </si>
+  <si>
+    <t>Vendor Invoice Intelligence System</t>
+  </si>
+  <si>
+    <t>Fake News Detection using Machine Learning</t>
+  </si>
+  <si>
+    <t>AQUACHECK AI (Water Potability Prediction using Machine Learning)</t>
+  </si>
+  <si>
+    <t>Air Quality Prediction</t>
+  </si>
+  <si>
+    <t>Machine Learning Based Stock Market Analysis and Price Movement Prediction System</t>
+  </si>
+  <si>
+    <t>"HandLex" - Sign Language Translations</t>
+  </si>
+  <si>
+    <t>Predictive Model for Diabetes Detection</t>
+  </si>
+  <si>
+    <t>sahilansari4590@gmail.com</t>
+  </si>
+  <si>
+    <t>8092675904</t>
+  </si>
+  <si>
+    <t>MD SAHIL JAMIR ANSARI</t>
+  </si>
+  <si>
+    <t>108427240037</t>
+  </si>
+  <si>
+    <t>Fashion Recommender System</t>
+  </si>
+  <si>
+    <t>108427240057</t>
+  </si>
+  <si>
+    <t>2617524445</t>
+  </si>
+  <si>
+    <t>ritika.mondal0808@gmail.com</t>
   </si>
 </sst>
 </file>
@@ -796,7 +817,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
   </numFmts>
   <fonts count="2" x14ac:knownFonts="1">
     <font>
@@ -833,11 +854,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -934,10 +957,10 @@
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="165" formatCode="m/d/yy\ h:mm:ss"/>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="m/d/yy\ h:mm:ss"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
@@ -956,8 +979,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AG16" totalsRowShown="0">
-  <autoFilter ref="A1:AG16" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="Table1" displayName="Table1" ref="A1:AG17" totalsRowShown="0">
+  <autoFilter ref="A1:AG17" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
   <tableColumns count="33">
     <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Group Number" dataDxfId="32"/>
     <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Start time" dataDxfId="31"/>
@@ -1294,7 +1317,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:AG16"/>
+  <dimension ref="A1:AG17"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="20" bestFit="1" customWidth="1"/>
@@ -1305,7 +1328,7 @@
   <sheetData>
     <row r="1" spans="1:33" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="B1" t="s">
         <v>0</v>
@@ -1421,37 +1444,37 @@
         <v>33</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I2" t="s">
+        <v>243</v>
+      </c>
+      <c r="J2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" t="s">
         <v>35</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
         <v>36</v>
       </c>
-      <c r="L2" t="s">
+      <c r="M2" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" t="s">
         <v>39</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>40</v>
       </c>
-      <c r="P2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>41</v>
-      </c>
-      <c r="Q2" s="2" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:33" x14ac:dyDescent="0.3">
@@ -1468,52 +1491,52 @@
         <v>32</v>
       </c>
       <c r="F3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I3" t="s">
+        <v>49</v>
+      </c>
+      <c r="J3" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" t="s">
         <v>51</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
         <v>52</v>
       </c>
-      <c r="L3" t="s">
+      <c r="M3" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="M3" s="2" t="s">
+      <c r="N3" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="N3" s="2" t="s">
+      <c r="O3" t="s">
         <v>55</v>
       </c>
-      <c r="O3" t="s">
+      <c r="P3" t="s">
         <v>56</v>
       </c>
-      <c r="P3" t="s">
+      <c r="Q3" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="Q3" s="2" t="s">
+      <c r="R3" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="R3" s="2" t="s">
+      <c r="S3" t="s">
         <v>59</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>60</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" s="2" t="s">
         <v>61</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="4" spans="1:33" x14ac:dyDescent="0.3">
@@ -1530,28 +1553,28 @@
         <v>32</v>
       </c>
       <c r="F4" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H4" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I4" t="s">
+        <v>244</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="K4" t="s">
         <v>63</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="L4" t="s">
         <v>64</v>
       </c>
-      <c r="K4" t="s">
+      <c r="M4" s="2" t="s">
         <v>65</v>
-      </c>
-      <c r="L4" t="s">
-        <v>66</v>
-      </c>
-      <c r="M4" s="2" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="5" spans="1:33" x14ac:dyDescent="0.3">
@@ -1568,28 +1591,28 @@
         <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G5" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H5" t="s">
+        <v>71</v>
+      </c>
+      <c r="I5" t="s">
+        <v>239</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="K5" t="s">
         <v>68</v>
       </c>
-      <c r="H5" t="s">
-        <v>73</v>
-      </c>
-      <c r="I5" t="s">
-        <v>247</v>
-      </c>
-      <c r="J5" s="2" t="s">
+      <c r="L5" t="s">
         <v>69</v>
       </c>
-      <c r="K5" t="s">
+      <c r="M5" s="2" t="s">
         <v>70</v>
-      </c>
-      <c r="L5" t="s">
-        <v>71</v>
-      </c>
-      <c r="M5" s="2" t="s">
-        <v>72</v>
       </c>
     </row>
     <row r="6" spans="1:33" x14ac:dyDescent="0.3">
@@ -1606,76 +1629,76 @@
         <v>32</v>
       </c>
       <c r="F6" t="s">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H6" t="s">
+        <v>71</v>
+      </c>
+      <c r="I6" t="s">
+        <v>240</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>72</v>
+      </c>
+      <c r="K6" t="s">
         <v>73</v>
       </c>
-      <c r="I6" t="s">
-        <v>248</v>
-      </c>
-      <c r="J6" s="2" t="s">
+      <c r="L6" t="s">
         <v>74</v>
       </c>
-      <c r="K6" t="s">
+      <c r="M6" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="L6" t="s">
+      <c r="N6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="M6" s="2" t="s">
+      <c r="O6" t="s">
         <v>77</v>
       </c>
-      <c r="N6" s="2" t="s">
+      <c r="P6" t="s">
         <v>78</v>
       </c>
-      <c r="O6" t="s">
+      <c r="Q6" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="P6" t="s">
+      <c r="R6" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="Q6" s="2" t="s">
+      <c r="S6" t="s">
         <v>81</v>
       </c>
-      <c r="R6" s="2" t="s">
+      <c r="T6" t="s">
         <v>82</v>
       </c>
-      <c r="S6" t="s">
+      <c r="U6" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="T6" t="s">
+      <c r="V6" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="U6" s="2" t="s">
+      <c r="W6" t="s">
         <v>85</v>
       </c>
-      <c r="V6" s="2" t="s">
+      <c r="X6" t="s">
         <v>86</v>
       </c>
-      <c r="W6" t="s">
+      <c r="Y6" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="X6" t="s">
+      <c r="Z6" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="Y6" s="2" t="s">
+      <c r="AA6" t="s">
         <v>89</v>
       </c>
-      <c r="Z6" s="2" t="s">
+      <c r="AB6" t="s">
         <v>90</v>
       </c>
-      <c r="AA6" t="s">
+      <c r="AC6" s="2" t="s">
         <v>91</v>
-      </c>
-      <c r="AB6" t="s">
-        <v>92</v>
-      </c>
-      <c r="AC6" s="2" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="7" spans="1:33" x14ac:dyDescent="0.3">
@@ -1692,28 +1715,28 @@
         <v>32</v>
       </c>
       <c r="F7" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H7" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I7" t="s">
+        <v>245</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="K7" t="s">
+        <v>93</v>
+      </c>
+      <c r="L7" t="s">
         <v>94</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="M7" s="2" t="s">
         <v>95</v>
-      </c>
-      <c r="K7" t="s">
-        <v>96</v>
-      </c>
-      <c r="L7" t="s">
-        <v>97</v>
-      </c>
-      <c r="M7" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="8" spans="1:33" x14ac:dyDescent="0.3">
@@ -1730,64 +1753,64 @@
         <v>32</v>
       </c>
       <c r="F8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H8" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I8" t="s">
+        <v>96</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="K8" t="s">
+        <v>98</v>
+      </c>
+      <c r="L8" t="s">
         <v>99</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="M8" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="K8" t="s">
+      <c r="N8" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="L8" t="s">
+      <c r="O8" t="s">
         <v>102</v>
       </c>
-      <c r="M8" s="2" t="s">
+      <c r="P8" t="s">
         <v>103</v>
       </c>
-      <c r="N8" s="2" t="s">
+      <c r="Q8" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="O8" t="s">
+      <c r="R8" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="P8" t="s">
+      <c r="S8" t="s">
         <v>106</v>
       </c>
-      <c r="Q8" s="2" t="s">
+      <c r="T8" t="s">
         <v>107</v>
       </c>
-      <c r="R8" s="2" t="s">
+      <c r="U8" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="S8" t="s">
+      <c r="V8" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="T8" t="s">
+      <c r="W8" t="s">
         <v>110</v>
       </c>
-      <c r="U8" s="2" t="s">
+      <c r="X8" t="s">
         <v>111</v>
       </c>
-      <c r="V8" s="2" t="s">
+      <c r="Y8" s="2" t="s">
         <v>112</v>
-      </c>
-      <c r="W8" t="s">
-        <v>113</v>
-      </c>
-      <c r="X8" t="s">
-        <v>114</v>
-      </c>
-      <c r="Y8" s="2" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="9" spans="1:33" x14ac:dyDescent="0.3">
@@ -1804,40 +1827,40 @@
         <v>32</v>
       </c>
       <c r="F9" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H9" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I9" t="s">
+        <v>254</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="K9" t="s">
+        <v>114</v>
+      </c>
+      <c r="L9" t="s">
+        <v>115</v>
+      </c>
+      <c r="M9" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="N9" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="K9" t="s">
+      <c r="O9" t="s">
         <v>118</v>
       </c>
-      <c r="L9" t="s">
+      <c r="P9" t="s">
         <v>119</v>
       </c>
-      <c r="M9" s="2" t="s">
+      <c r="Q9" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="N9" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="O9" t="s">
-        <v>122</v>
-      </c>
-      <c r="P9" t="s">
-        <v>123</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>124</v>
       </c>
     </row>
     <row r="10" spans="1:33" x14ac:dyDescent="0.3">
@@ -1854,64 +1877,64 @@
         <v>32</v>
       </c>
       <c r="F10" t="s">
+        <v>121</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H10" t="s">
+        <v>71</v>
+      </c>
+      <c r="I10" t="s">
+        <v>122</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="K10" t="s">
+        <v>124</v>
+      </c>
+      <c r="L10" t="s">
         <v>125</v>
       </c>
-      <c r="G10" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H10" t="s">
-        <v>73</v>
-      </c>
-      <c r="I10" t="s">
+      <c r="M10" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="N10" s="2" t="s">
         <v>127</v>
       </c>
-      <c r="K10" t="s">
+      <c r="O10" t="s">
         <v>128</v>
       </c>
-      <c r="L10" t="s">
+      <c r="P10" t="s">
         <v>129</v>
       </c>
-      <c r="M10" s="2" t="s">
+      <c r="Q10" s="2" t="s">
         <v>130</v>
       </c>
-      <c r="N10" s="2" t="s">
+      <c r="R10" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="O10" t="s">
+      <c r="S10" t="s">
         <v>132</v>
       </c>
-      <c r="P10" t="s">
+      <c r="T10" t="s">
         <v>133</v>
       </c>
-      <c r="Q10" s="2" t="s">
+      <c r="U10" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="R10" s="2" t="s">
+      <c r="V10" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="S10" t="s">
+      <c r="W10" t="s">
         <v>136</v>
       </c>
-      <c r="T10" t="s">
+      <c r="X10" t="s">
         <v>137</v>
       </c>
-      <c r="U10" s="2" t="s">
+      <c r="Y10" s="2" t="s">
         <v>138</v>
-      </c>
-      <c r="V10" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="W10" t="s">
-        <v>140</v>
-      </c>
-      <c r="X10" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y10" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="11" spans="1:33" x14ac:dyDescent="0.3">
@@ -1928,88 +1951,88 @@
         <v>32</v>
       </c>
       <c r="F11" t="s">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H11" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I11" t="s">
+        <v>247</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="K11" t="s">
+        <v>140</v>
+      </c>
+      <c r="L11" t="s">
+        <v>141</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="N11" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="O11" t="s">
         <v>144</v>
       </c>
-      <c r="K11" t="s">
+      <c r="P11" t="s">
         <v>145</v>
       </c>
-      <c r="L11" t="s">
+      <c r="Q11" s="2" t="s">
         <v>146</v>
       </c>
-      <c r="M11" s="2" t="s">
+      <c r="R11" s="2" t="s">
         <v>147</v>
       </c>
-      <c r="N11" s="2" t="s">
+      <c r="S11" t="s">
         <v>148</v>
       </c>
-      <c r="O11" t="s">
+      <c r="T11" t="s">
         <v>149</v>
       </c>
-      <c r="P11" t="s">
+      <c r="U11" s="2" t="s">
         <v>150</v>
       </c>
-      <c r="Q11" s="2" t="s">
+      <c r="V11" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="R11" s="2" t="s">
+      <c r="W11" t="s">
         <v>152</v>
       </c>
-      <c r="S11" t="s">
+      <c r="X11" t="s">
         <v>153</v>
       </c>
-      <c r="T11" t="s">
+      <c r="Y11" s="2" t="s">
         <v>154</v>
       </c>
-      <c r="U11" s="2" t="s">
+      <c r="Z11" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="AA11" t="s">
         <v>155</v>
       </c>
-      <c r="V11" s="2" t="s">
+      <c r="AB11" t="s">
         <v>156</v>
       </c>
-      <c r="W11" t="s">
+      <c r="AC11" s="2" t="s">
         <v>157</v>
       </c>
-      <c r="X11" t="s">
+      <c r="AD11" s="2" t="s">
         <v>158</v>
       </c>
-      <c r="Y11" s="2" t="s">
+      <c r="AE11" t="s">
         <v>159</v>
       </c>
-      <c r="Z11" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="AA11" t="s">
+      <c r="AF11" t="s">
         <v>160</v>
       </c>
-      <c r="AB11" t="s">
+      <c r="AG11" s="2" t="s">
         <v>161</v>
-      </c>
-      <c r="AC11" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="AD11" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="AE11" t="s">
-        <v>164</v>
-      </c>
-      <c r="AF11" t="s">
-        <v>165</v>
-      </c>
-      <c r="AG11" s="2" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="12" spans="1:33" x14ac:dyDescent="0.3">
@@ -2026,76 +2049,76 @@
         <v>32</v>
       </c>
       <c r="F12" t="s">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I12" t="s">
+        <v>246</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>162</v>
+      </c>
+      <c r="K12" t="s">
+        <v>163</v>
+      </c>
+      <c r="L12" t="s">
+        <v>164</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>165</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="O12" t="s">
         <v>167</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="P12" t="s">
         <v>168</v>
       </c>
-      <c r="K12" t="s">
+      <c r="Q12" s="2" t="s">
         <v>169</v>
       </c>
-      <c r="L12" t="s">
+      <c r="R12" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="M12" s="2" t="s">
+      <c r="S12" t="s">
         <v>171</v>
       </c>
-      <c r="N12" s="2" t="s">
+      <c r="T12" t="s">
         <v>172</v>
       </c>
-      <c r="O12" t="s">
+      <c r="U12" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="P12" t="s">
+      <c r="V12" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="Q12" s="2" t="s">
+      <c r="W12" t="s">
         <v>175</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="X12" t="s">
         <v>176</v>
       </c>
-      <c r="S12" t="s">
+      <c r="Y12" s="2" t="s">
         <v>177</v>
       </c>
-      <c r="T12" t="s">
+      <c r="Z12" s="2" t="s">
         <v>178</v>
       </c>
-      <c r="U12" s="2" t="s">
+      <c r="AA12" t="s">
         <v>179</v>
       </c>
-      <c r="V12" s="2" t="s">
+      <c r="AB12" t="s">
         <v>180</v>
       </c>
-      <c r="W12" t="s">
+      <c r="AC12" s="2" t="s">
         <v>181</v>
-      </c>
-      <c r="X12" t="s">
-        <v>182</v>
-      </c>
-      <c r="Y12" s="2" t="s">
-        <v>183</v>
-      </c>
-      <c r="Z12" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="AA12" t="s">
-        <v>185</v>
-      </c>
-      <c r="AB12" t="s">
-        <v>186</v>
-      </c>
-      <c r="AC12" s="2" t="s">
-        <v>187</v>
       </c>
     </row>
     <row r="13" spans="1:33" x14ac:dyDescent="0.3">
@@ -2112,88 +2135,88 @@
         <v>32</v>
       </c>
       <c r="F13" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H13" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I13" t="s">
+        <v>182</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="K13" t="s">
+        <v>184</v>
+      </c>
+      <c r="L13" t="s">
+        <v>185</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>187</v>
+      </c>
+      <c r="O13" t="s">
         <v>188</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="P13" t="s">
         <v>189</v>
       </c>
-      <c r="K13" t="s">
+      <c r="Q13" s="2" t="s">
         <v>190</v>
       </c>
-      <c r="L13" t="s">
+      <c r="R13" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="M13" s="2" t="s">
+      <c r="S13" t="s">
         <v>192</v>
       </c>
-      <c r="N13" s="2" t="s">
+      <c r="T13" t="s">
         <v>193</v>
       </c>
-      <c r="O13" t="s">
+      <c r="U13" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="P13" t="s">
+      <c r="V13" t="s">
         <v>195</v>
       </c>
-      <c r="Q13" s="2" t="s">
+      <c r="W13" t="s">
         <v>196</v>
       </c>
-      <c r="R13" s="2" t="s">
+      <c r="X13" t="s">
         <v>197</v>
       </c>
-      <c r="S13" t="s">
+      <c r="Y13" t="s">
         <v>198</v>
       </c>
-      <c r="T13" t="s">
+      <c r="Z13" s="2" t="s">
         <v>199</v>
       </c>
-      <c r="U13" s="2" t="s">
+      <c r="AA13" t="s">
         <v>200</v>
       </c>
-      <c r="V13" t="s">
+      <c r="AB13" t="s">
         <v>201</v>
       </c>
-      <c r="W13" t="s">
+      <c r="AC13" t="s">
         <v>202</v>
       </c>
-      <c r="X13" t="s">
+      <c r="AD13" t="s">
         <v>203</v>
       </c>
-      <c r="Y13" t="s">
+      <c r="AE13" t="s">
         <v>204</v>
       </c>
-      <c r="Z13" s="2" t="s">
+      <c r="AF13" t="s">
         <v>205</v>
       </c>
-      <c r="AA13" t="s">
+      <c r="AG13" t="s">
         <v>206</v>
-      </c>
-      <c r="AB13" t="s">
-        <v>207</v>
-      </c>
-      <c r="AC13" t="s">
-        <v>208</v>
-      </c>
-      <c r="AD13" t="s">
-        <v>209</v>
-      </c>
-      <c r="AE13" t="s">
-        <v>210</v>
-      </c>
-      <c r="AF13" t="s">
-        <v>211</v>
-      </c>
-      <c r="AG13" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="14" spans="1:33" x14ac:dyDescent="0.3">
@@ -2210,34 +2233,40 @@
         <v>32</v>
       </c>
       <c r="F14" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H14" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I14" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="J14" s="3" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="K14" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="L14" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="M14" s="2" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="N14" s="2" t="s">
-        <v>216</v>
+        <v>255</v>
       </c>
       <c r="O14" t="s">
-        <v>217</v>
+        <v>210</v>
+      </c>
+      <c r="P14" t="s">
+        <v>257</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="15" spans="1:33" x14ac:dyDescent="0.3">
@@ -2254,28 +2283,28 @@
         <v>32</v>
       </c>
       <c r="F15" t="s">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H15" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="I15" t="s">
-        <v>218</v>
+        <v>211</v>
       </c>
       <c r="J15" s="2" t="s">
-        <v>219</v>
+        <v>212</v>
       </c>
       <c r="K15" t="s">
-        <v>220</v>
+        <v>213</v>
       </c>
       <c r="L15" t="s">
-        <v>221</v>
+        <v>214</v>
       </c>
       <c r="M15" s="2" t="s">
-        <v>222</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:33" x14ac:dyDescent="0.3">
@@ -2292,96 +2321,147 @@
         <v>32</v>
       </c>
       <c r="F16" t="s">
+        <v>42</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" t="s">
+        <v>71</v>
+      </c>
+      <c r="I16" t="s">
+        <v>216</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="K16" t="s">
+        <v>218</v>
+      </c>
+      <c r="L16" t="s">
+        <v>219</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="O16" t="s">
+        <v>222</v>
+      </c>
+      <c r="P16" t="s">
+        <v>223</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="S16" t="s">
+        <v>226</v>
+      </c>
+      <c r="T16" t="s">
+        <v>227</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="V16" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="W16" t="s">
+        <v>230</v>
+      </c>
+      <c r="X16" t="s">
+        <v>231</v>
+      </c>
+      <c r="Y16" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="Z16" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="G16" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="H16" t="s">
-        <v>73</v>
-      </c>
-      <c r="I16" t="s">
-        <v>223</v>
-      </c>
-      <c r="J16" s="2" t="s">
-        <v>224</v>
-      </c>
-      <c r="K16" t="s">
-        <v>225</v>
-      </c>
-      <c r="L16" t="s">
-        <v>226</v>
-      </c>
-      <c r="M16" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="N16" s="2" t="s">
-        <v>228</v>
-      </c>
-      <c r="O16" t="s">
-        <v>229</v>
-      </c>
-      <c r="P16" t="s">
-        <v>230</v>
-      </c>
-      <c r="Q16" s="2" t="s">
-        <v>231</v>
-      </c>
-      <c r="R16" s="2" t="s">
-        <v>232</v>
-      </c>
-      <c r="S16" t="s">
+      <c r="AA16" t="s">
         <v>233</v>
       </c>
-      <c r="T16" t="s">
+      <c r="AB16" t="s">
+        <v>44</v>
+      </c>
+      <c r="AC16" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="AD16" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="AE16" t="s">
         <v>234</v>
       </c>
-      <c r="U16" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="V16" s="2" t="s">
-        <v>236</v>
-      </c>
-      <c r="W16" t="s">
-        <v>237</v>
-      </c>
-      <c r="X16" t="s">
-        <v>238</v>
-      </c>
-      <c r="Y16" s="2" t="s">
-        <v>239</v>
-      </c>
-      <c r="Z16" s="2" t="s">
-        <v>44</v>
-      </c>
-      <c r="AA16" t="s">
-        <v>240</v>
-      </c>
-      <c r="AB16" t="s">
-        <v>45</v>
-      </c>
-      <c r="AC16" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="AD16" s="2" t="s">
+      <c r="AF16" t="s">
         <v>47</v>
       </c>
-      <c r="AE16" t="s">
-        <v>241</v>
-      </c>
-      <c r="AF16" t="s">
+      <c r="AG16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="AG16" s="2" t="s">
-        <v>49</v>
-      </c>
+    </row>
+    <row r="17" spans="1:33" x14ac:dyDescent="0.3">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="4"/>
+      <c r="E17" s="4"/>
+      <c r="F17" s="4"/>
+      <c r="G17" s="4"/>
+      <c r="H17" s="4"/>
+      <c r="I17" s="4" t="s">
+        <v>249</v>
+      </c>
+      <c r="J17" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="K17" s="4" t="s">
+        <v>252</v>
+      </c>
+      <c r="L17" t="s">
+        <v>250</v>
+      </c>
+      <c r="M17" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="N17" s="4"/>
+      <c r="O17" s="4"/>
+      <c r="P17" s="4"/>
+      <c r="Q17" s="4"/>
+      <c r="R17" s="4"/>
+      <c r="S17" s="4"/>
+      <c r="T17" s="4"/>
+      <c r="U17" s="4"/>
+      <c r="V17" s="4"/>
+      <c r="W17" s="4"/>
+      <c r="X17" s="4"/>
+      <c r="Y17" s="4"/>
+      <c r="Z17" s="4"/>
+      <c r="AA17" s="4"/>
+      <c r="AB17" s="4"/>
+      <c r="AC17" s="4"/>
+      <c r="AD17" s="4"/>
+      <c r="AE17" s="4"/>
+      <c r="AF17" s="4"/>
+      <c r="AG17" s="4"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
+  <hyperlinks>
+    <hyperlink ref="L17" r:id="rId1" xr:uid="{71BB7201-B71B-411D-A5A5-06F37C0F6615}"/>
+    <hyperlink ref="P14" r:id="rId2" xr:uid="{14DEB8B8-78CA-45CA-ACD8-E8BAEF4344E0}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId3"/>
   <tableParts count="1">
-    <tablePart r:id="rId2"/>
+    <tablePart r:id="rId4"/>
   </tableParts>
 </worksheet>
 </file>